--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,402 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129174137</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91523</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västra Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>694967</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6618904</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129174144</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694967</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618904</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129174136</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91523</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694901</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618834</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129174141</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra Ledinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694840</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618766</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Riala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129174144</v>
       </c>
       <c r="B4" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129174141</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129174144</v>
       </c>
       <c r="B4" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129174141</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25687-2025 artfynd.xlsx
+++ b/artfynd/A 25687-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129174137</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>129174144</v>
       </c>
       <c r="B4" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129174136</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>129174141</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
